--- a/data/trans_dic/P16A_2_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 30,51</t>
+          <t>23,39; 30,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,62; 41,04</t>
+          <t>28,8; 41,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 35,18</t>
+          <t>28,58; 35,14</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 22,52</t>
+          <t>8,12; 22,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 41,76</t>
+          <t>36,57; 41,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 30,87</t>
+          <t>18,03; 30,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 26,45</t>
+          <t>19,29; 26,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,17; 72,76</t>
+          <t>34,03; 74,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 59,43</t>
+          <t>28,44; 58,43</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,1; 28,23</t>
+          <t>22,16; 28,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,21; 41,37</t>
+          <t>30,38; 41,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 34,37</t>
+          <t>28,22; 34,24</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 24,48</t>
+          <t>17,33; 24,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,85; 52,44</t>
+          <t>36,94; 52,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 38,45</t>
+          <t>28,84; 37,7</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>146945; 193888</t>
+          <t>148634; 196515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>207594; 297693</t>
+          <t>208882; 297983</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>385667; 478667</t>
+          <t>388951; 478125</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112118; 268582</t>
+          <t>96834; 266199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>348324; 400378</t>
+          <t>350613; 400667</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>394523; 664097</t>
+          <t>387909; 664808</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>136714; 186370</t>
+          <t>135928; 187691</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>318961; 679085</t>
+          <t>317616; 696846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466543; 973452</t>
+          <t>465883; 957125</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>204852; 261603</t>
+          <t>205352; 262832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>330820; 452957</t>
+          <t>332695; 455389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570831; 694895</t>
+          <t>570474; 692350</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>594040; 847131</t>
+          <t>599658; 852926</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1367959; 1946538</t>
+          <t>1371287; 1936484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2059043; 2757995</t>
+          <t>2068179; 2703878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_2_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 30,93</t>
+          <t>23,4; 30,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,8; 41,08</t>
+          <t>36,69; 42,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,58; 35,14</t>
+          <t>31,22; 35,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 22,32</t>
+          <t>18,31; 23,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 41,79</t>
+          <t>36,21; 41,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 30,9</t>
+          <t>27,99; 31,82</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,29; 26,63</t>
+          <t>19,22; 25,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,03; 74,66</t>
+          <t>33,09; 39,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,44; 58,43</t>
+          <t>26,99; 31,48</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 28,36</t>
+          <t>21,95; 27,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 41,59</t>
+          <t>37,0; 42,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,22; 34,24</t>
+          <t>30,61; 34,3</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 24,65</t>
+          <t>21,95; 25,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 52,16</t>
+          <t>37,21; 39,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,84; 37,7</t>
+          <t>30,12; 32,29</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>171183</t>
+          <t>187399</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>269521</t>
+          <t>288764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440705</t>
+          <t>476163</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>148634; 196515</t>
+          <t>161638; 212243</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>208882; 297983</t>
+          <t>269376; 309520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388951; 478125</t>
+          <t>444856; 510484</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>220288</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374375</t>
+          <t>414652</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577783</t>
+          <t>634940</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96834; 266199</t>
+          <t>192102; 249540</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350613; 400667</t>
+          <t>388000; 442138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>387909; 664808</t>
+          <t>593568; 674804</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>160632</t>
+          <t>178478</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>464539</t>
+          <t>293310</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625171</t>
+          <t>471787</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>135928; 187691</t>
+          <t>154383; 206246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>317616; 696846</t>
+          <t>268796; 317696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>465883; 957125</t>
+          <t>435954; 508491</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>231677</t>
+          <t>241870</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>413519</t>
+          <t>442915</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>645196</t>
+          <t>684785</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>205352; 262832</t>
+          <t>217275; 270156</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>332695; 455389</t>
+          <t>413991; 471451</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570474; 692350</t>
+          <t>645620; 723492</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>599658; 852926</t>
+          <t>775545; 887853</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1371287; 1936484</t>
+          <t>1390477; 1492474</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2068179; 2703878</t>
+          <t>2189604; 2347341</t>
         </is>
       </c>
     </row>
